--- a/output/yearly_surface_area_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_15_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497654523242</v>
+        <v>10.84497655263382</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907268416363</v>
+        <v>37.78907270995363</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.660356352059609</v>
+        <v>5.363287708300325</v>
       </c>
       <c r="C2" t="n">
-        <v>10.18268718844792</v>
+        <v>9.908779578963058</v>
       </c>
       <c r="D2" t="n">
-        <v>29.35621985238812</v>
+        <v>29.92170653003429</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.78297700409922</v>
+        <v>19.03608798534566</v>
       </c>
       <c r="C3" t="n">
-        <v>51.42885348696916</v>
+        <v>47.50677140850316</v>
       </c>
       <c r="D3" t="n">
-        <v>77.59733854366789</v>
+        <v>76.7481267794944</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.48937768726719</v>
+        <v>38.5817030291954</v>
       </c>
       <c r="C4" t="n">
-        <v>107.6024936285632</v>
+        <v>86.07178472672636</v>
       </c>
       <c r="D4" t="n">
-        <v>98.98765752379741</v>
+        <v>93.99743394311086</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.31332605303754</v>
+        <v>46.06851102178158</v>
       </c>
       <c r="C5" t="n">
-        <v>172.4439842509523</v>
+        <v>135.9720570381833</v>
       </c>
       <c r="D5" t="n">
-        <v>73.63107781851079</v>
+        <v>65.58074664368695</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.56108632740622</v>
+        <v>40.57366912111219</v>
       </c>
       <c r="C6" t="n">
-        <v>163.1802129136794</v>
+        <v>147.0795505640317</v>
       </c>
       <c r="D6" t="n">
-        <v>46.97368240509714</v>
+        <v>46.08814597586652</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="C7" t="n">
-        <v>126.4805202335251</v>
+        <v>129.7742837812731</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>13.60211444233956</v>
       </c>
       <c r="C8" t="n">
-        <v>73.01748550335651</v>
+        <v>86.61959994569608</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.654343563473552</v>
+        <v>7.658786659856551</v>
       </c>
       <c r="C21" t="n">
-        <v>92.80891570711681</v>
+        <v>92.86278825076069</v>
       </c>
       <c r="D21" t="n">
-        <v>7.654343563473552</v>
+        <v>7.658786659856551</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.639559723821178</v>
+        <v>6.590472338608838</v>
       </c>
       <c r="C2" t="n">
-        <v>6.749515466696821</v>
+        <v>15.90038581798134</v>
       </c>
       <c r="D2" t="n">
-        <v>24.3620692808846</v>
+        <v>33.4285093296039</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.98776136365931</v>
+        <v>18.25559856046944</v>
       </c>
       <c r="C3" t="n">
-        <v>45.39601384437251</v>
+        <v>42.7992911666397</v>
       </c>
       <c r="D3" t="n">
-        <v>81.36234098945442</v>
+        <v>81.03836424705297</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.46836007485052</v>
+        <v>36.82044764777662</v>
       </c>
       <c r="C4" t="n">
-        <v>115.8599735689831</v>
+        <v>100.3405058602495</v>
       </c>
       <c r="D4" t="n">
-        <v>111.7631403991611</v>
+        <v>106.4410860944392</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>50.82998738737862</v>
       </c>
       <c r="C5" t="n">
-        <v>182.0896554451772</v>
+        <v>146.1822331623501</v>
       </c>
       <c r="D5" t="n">
-        <v>87.47372044839082</v>
+        <v>81.26416621902975</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.20890094348888</v>
+        <v>49.79129831628549</v>
       </c>
       <c r="C6" t="n">
-        <v>212.2067297683566</v>
+        <v>176.3425043845164</v>
       </c>
       <c r="D6" t="n">
-        <v>56.95609306187872</v>
+        <v>53.85671555957153</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.33309987584271</v>
+        <v>36.29128563518759</v>
       </c>
       <c r="C7" t="n">
-        <v>173.0124161717111</v>
+        <v>165.9457961965426</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.86213871524472</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>114.407968714402</v>
+        <v>125.3397294011903</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>60.12811989430013</v>
+        <v>73.66249374504666</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
         <v>35.16129402759952</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.819469151317258</v>
+        <v>7.827821240408505</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6756653232097</v>
+        <v>100.7831984702595</v>
       </c>
       <c r="D21" t="n">
-        <v>8.796902795231915</v>
+        <v>8.806298895459568</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.068583470577035</v>
+        <v>7.158904259367741</v>
       </c>
       <c r="C2" t="n">
-        <v>7.354272052512856</v>
+        <v>13.17603593869644</v>
       </c>
       <c r="D2" t="n">
-        <v>19.21771131063131</v>
+        <v>29.7940793284822</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.14760631300229</v>
+        <v>19.33552103514093</v>
       </c>
       <c r="C3" t="n">
-        <v>36.6142806298848</v>
+        <v>51.17850782238622</v>
       </c>
       <c r="D3" t="n">
-        <v>80.8125622750762</v>
+        <v>85.62312602588557</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.64329109265569</v>
+        <v>34.85498874387451</v>
       </c>
       <c r="C4" t="n">
-        <v>114.3156844302029</v>
+        <v>101.6933541967016</v>
       </c>
       <c r="D4" t="n">
-        <v>120.6970445078071</v>
+        <v>116.1918042930185</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.11759840699392</v>
+        <v>51.95899724726245</v>
       </c>
       <c r="C5" t="n">
-        <v>192.1771131063132</v>
+        <v>160.147594255261</v>
       </c>
       <c r="D5" t="n">
-        <v>101.9299553934251</v>
+        <v>94.59139130418019</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.08564270111029</v>
+        <v>56.67433147075987</v>
       </c>
       <c r="C6" t="n">
-        <v>240.704902127233</v>
+        <v>197.474623718429</v>
       </c>
       <c r="D6" t="n">
-        <v>66.45548384817086</v>
+        <v>63.79887456047898</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.51949307092936</v>
+        <v>45.03473068920969</v>
       </c>
       <c r="C7" t="n">
-        <v>224.3352409066217</v>
+        <v>202.7161747114026</v>
       </c>
       <c r="D7" t="n">
-        <v>47.49008169753095</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.37112599440107</v>
       </c>
       <c r="C8" t="n">
-        <v>160.2212253330794</v>
+        <v>162.3908877594649</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.31093628480575</v>
+        <v>13.7562488319063</v>
       </c>
       <c r="C9" t="n">
-        <v>90.96874227550941</v>
+        <v>105.6124910320548</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>60.21549543997811</v>
       </c>
       <c r="D10" t="n">
         <v>35.87306111317846</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>39.44858625204532</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.96721518819316</v>
+        <v>7.978984375821277</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5574050406076</v>
+        <v>107.7162890735872</v>
       </c>
       <c r="D21" t="n">
-        <v>9.95901898524145</v>
+        <v>9.973730469776596</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.557092916664446</v>
+        <v>6.656249434793374</v>
       </c>
       <c r="C2" t="n">
-        <v>5.235660506748239</v>
+        <v>9.275552309723864</v>
       </c>
       <c r="D2" t="n">
-        <v>16.30486587213103</v>
+        <v>24.8215272064721</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.01921834792421</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="C3" t="n">
-        <v>57.80039608753097</v>
+        <v>72.72786993060372</v>
       </c>
       <c r="D3" t="n">
-        <v>87.63080008107029</v>
+        <v>91.42034621946299</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.15608218944201</v>
+        <v>24.96388062358789</v>
       </c>
       <c r="C4" t="n">
-        <v>155.1946770873358</v>
+        <v>132.6557132932375</v>
       </c>
       <c r="D4" t="n">
-        <v>114.7751423557904</v>
+        <v>109.1978336479642</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.32971266437347</v>
+        <v>31.90680038802134</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8260386721578</v>
+        <v>117.9815303578605</v>
       </c>
       <c r="D5" t="n">
-        <v>66.1207078810227</v>
+        <v>62.63550353094652</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.40508625342222</v>
+        <v>27.93464917663875</v>
       </c>
       <c r="C6" t="n">
-        <v>147.7638287138917</v>
+        <v>133.5147425344535</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>112.6467133329833</v>
+        <v>114.2037651919187</v>
       </c>
       <c r="D7" t="n">
-        <v>27.72750041104266</v>
+        <v>28.32636651063322</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>67.00918955336604</v>
+        <v>77.77405313043232</v>
       </c>
       <c r="D8" t="n">
-        <v>26.53664044579129</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1814,7 +1814,7 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>45.92812110007426</v>
       </c>
       <c r="D9" t="n">
         <v>27.29062268265283</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.12726734865359</v>
+        <v>4.085052197370977</v>
       </c>
       <c r="C2" t="n">
-        <v>4.049709280018093</v>
+        <v>4.57985304031137</v>
       </c>
       <c r="D2" t="n">
-        <v>11.58560465781661</v>
+        <v>17.58899186928585</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.14331946928681</v>
+        <v>23.60612354861455</v>
       </c>
       <c r="C3" t="n">
-        <v>40.22220344299183</v>
+        <v>55.88107932572845</v>
       </c>
       <c r="D3" t="n">
-        <v>81.94157213496004</v>
+        <v>90.48277716190728</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.43083267791088</v>
+        <v>32.87676711981719</v>
       </c>
       <c r="C4" t="n">
-        <v>155.756236774165</v>
+        <v>159.9041208246077</v>
       </c>
       <c r="D4" t="n">
-        <v>129.7585758180052</v>
+        <v>126.4657940179614</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.44676162535709</v>
+        <v>35.63744166415923</v>
       </c>
       <c r="C5" t="n">
-        <v>205.7252314249192</v>
+        <v>172.7139648696201</v>
       </c>
       <c r="D5" t="n">
-        <v>83.17857424231102</v>
+        <v>78.9079717288374</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>32.56358960216246</v>
       </c>
       <c r="C6" t="n">
-        <v>185.5601335796897</v>
+        <v>161.2481334317216</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>147.6803801590307</v>
+        <v>143.7877505116921</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3625112492411</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>90.79202768874502</v>
+        <v>101.8906854852552</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2184,7 +2184,7 @@
         <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.501313223971626</v>
+        <v>3.627557767191965</v>
       </c>
       <c r="C2" t="n">
-        <v>5.64504929941916</v>
+        <v>4.936227456952962</v>
       </c>
       <c r="D2" t="n">
-        <v>13.61782240560751</v>
+        <v>20.82090531166635</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.10833640483242</v>
+        <v>18.80046853632642</v>
       </c>
       <c r="C3" t="n">
-        <v>28.01417074068273</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D3" t="n">
-        <v>73.95505456091222</v>
+        <v>84.9211764173491</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.17405674775472</v>
+        <v>38.31368590593603</v>
       </c>
       <c r="C4" t="n">
-        <v>128.9289990079166</v>
+        <v>149.8343346221482</v>
       </c>
       <c r="D4" t="n">
-        <v>138.6031408855647</v>
+        <v>139.3306159344116</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.13460691313561</v>
+        <v>41.11068511533519</v>
       </c>
       <c r="C5" t="n">
-        <v>242.8598383380548</v>
+        <v>228.624496626476</v>
       </c>
       <c r="D5" t="n">
-        <v>104.6052178874977</v>
+        <v>99.40195505498957</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.54850353370026</v>
+        <v>39.40637110076273</v>
       </c>
       <c r="C6" t="n">
-        <v>249.801776354784</v>
+        <v>212.8507562623425</v>
       </c>
       <c r="D6" t="n">
-        <v>51.11960296013142</v>
+        <v>50.11331156327844</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="C7" t="n">
-        <v>199.1828647238184</v>
+        <v>182.2948407153647</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>34.2551408965797</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>135.5204530942297</v>
+        <v>140.4439178310274</v>
       </c>
       <c r="D8" t="n">
-        <v>28.70630287217673</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2436,10 +2436,10 @@
         <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>69.11405663127118</v>
+        <v>79.87499321752047</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>38.15071578703105</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2495,7 +2495,7 @@
         <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.748893571891069</v>
+        <v>2.23445777486574</v>
       </c>
       <c r="C2" t="n">
-        <v>2.774419012201486</v>
+        <v>2.440624792757571</v>
       </c>
       <c r="D2" t="n">
-        <v>9.634871969478198</v>
+        <v>14.70559886191297</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.40776945462769</v>
+        <v>18.02488784997144</v>
       </c>
       <c r="C3" t="n">
-        <v>27.36130851735861</v>
+        <v>32.12278488295564</v>
       </c>
       <c r="D3" t="n">
-        <v>71.84920573530282</v>
+        <v>84.99480749516761</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.47960126795373</v>
+        <v>41.75962034784233</v>
       </c>
       <c r="C4" t="n">
-        <v>121.9222656427071</v>
+        <v>145.0355518437898</v>
       </c>
       <c r="D4" t="n">
-        <v>146.1969593779138</v>
+        <v>149.0302832523701</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.36179154344412</v>
+        <v>42.11697651218817</v>
       </c>
       <c r="C5" t="n">
-        <v>283.3078437530233</v>
+        <v>277.8100566092412</v>
       </c>
       <c r="D5" t="n">
-        <v>107.1823056111456</v>
+        <v>102.2490233973053</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.06169554111408</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="C6" t="n">
-        <v>282.6068758921911</v>
+        <v>241.1074186859742</v>
       </c>
       <c r="D6" t="n">
-        <v>49.79129831628549</v>
+        <v>49.06676851055134</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.785259294677205</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>194.511709147012</v>
+        <v>186.2473569726624</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>89.45685081096936</v>
+        <v>98.71964040053801</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2792,7 +2792,7 @@
         <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.061089341841555</v>
+        <v>2.691952205044754</v>
       </c>
       <c r="C2" t="n">
-        <v>4.855724145204724</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="D2" t="n">
-        <v>11.84282255632927</v>
+        <v>11.72501283181966</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16661937228147</v>
+        <v>13.06706194352505</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39933463591697</v>
+        <v>21.24011158137974</v>
       </c>
       <c r="D3" t="n">
-        <v>64.10321634879548</v>
+        <v>78.7656183117216</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.05017661057038</v>
+        <v>38.60722846950582</v>
       </c>
       <c r="C4" t="n">
-        <v>96.95838501911925</v>
+        <v>114.8517186767216</v>
       </c>
       <c r="D4" t="n">
-        <v>149.3876394167159</v>
+        <v>154.8500836431452</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.9703362513569</v>
+        <v>50.19185137961819</v>
       </c>
       <c r="C5" t="n">
-        <v>259.5004619250382</v>
+        <v>275.1593378077748</v>
       </c>
       <c r="D5" t="n">
-        <v>127.283589855599</v>
+        <v>123.8965602759475</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>39.72838434775569</v>
       </c>
       <c r="C6" t="n">
-        <v>354.5768365951163</v>
+        <v>325.7969026451211</v>
       </c>
       <c r="D6" t="n">
-        <v>64.84541761320608</v>
+        <v>63.23535137824131</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>16.22927129890402</v>
       </c>
       <c r="C7" t="n">
-        <v>282.3653659569464</v>
+        <v>254.0389994463131</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>151.6260241823986</v>
+        <v>154.129480828228</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>62.56874468705769</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3103,7 +3103,7 @@
         <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.005710559776233</v>
+        <v>1.858448404139212</v>
       </c>
       <c r="C2" t="n">
-        <v>3.578470381979624</v>
+        <v>3.408628029144925</v>
       </c>
       <c r="D2" t="n">
-        <v>9.440485924037329</v>
+        <v>9.953939973358411</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.7283589855599</v>
+        <v>11.56989669454866</v>
       </c>
       <c r="C3" t="n">
-        <v>19.51714436042659</v>
+        <v>20.85722997672349</v>
       </c>
       <c r="D3" t="n">
-        <v>60.16640805476577</v>
+        <v>72.34989706446869</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.03817465394117</v>
+        <v>34.12751369502762</v>
       </c>
       <c r="C4" t="n">
-        <v>79.38411936539708</v>
+        <v>93.43587425628169</v>
       </c>
       <c r="D4" t="n">
-        <v>148.4304354050753</v>
+        <v>159.3425611377786</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.36365722786139</v>
+        <v>54.38882281527331</v>
       </c>
       <c r="C5" t="n">
-        <v>239.5218961436156</v>
+        <v>259.623180388069</v>
       </c>
       <c r="D5" t="n">
-        <v>142.7461161974863</v>
+        <v>138.0091835244954</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.10323204432872</v>
+        <v>45.28311285838414</v>
       </c>
       <c r="C6" t="n">
-        <v>389.5152738938518</v>
+        <v>374.6624128763019</v>
       </c>
       <c r="D6" t="n">
-        <v>76.3976428490783</v>
+        <v>74.46556336712058</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.07335334037803</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>354.4688443476491</v>
+        <v>321.0521159904962</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>43.29801900039708</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>198.6075605691297</v>
+        <v>196.2710010330223</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4609323660398</v>
+        <v>66.56249434793372</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
         <v>24.76949457814703</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.85664913964673</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
         <v>19.52696183746906</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.909900195387546</v>
+        <v>2.78227299383546</v>
       </c>
       <c r="C2" t="n">
-        <v>8.205447312094842</v>
+        <v>8.239808481743479</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8206843274881</v>
+        <v>16.13306002388784</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.989282890711296</v>
+        <v>9.130253649495335</v>
       </c>
       <c r="C3" t="n">
-        <v>17.06277509980957</v>
+        <v>17.40147805777471</v>
       </c>
       <c r="D3" t="n">
-        <v>54.95823648373645</v>
+        <v>65.30585728649783</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.3032054763588</v>
+        <v>28.51191682673587</v>
       </c>
       <c r="C4" t="n">
-        <v>66.45548384817084</v>
+        <v>76.05304940488766</v>
       </c>
       <c r="D4" t="n">
-        <v>144.984500963169</v>
+        <v>158.3598316858275</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.31456984264904</v>
+        <v>53.50524988145118</v>
       </c>
       <c r="C5" t="n">
-        <v>202.0191338413875</v>
+        <v>224.2802630351839</v>
       </c>
       <c r="D5" t="n">
-        <v>156.1960597456676</v>
+        <v>154.821612959722</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.91834468076083</v>
+        <v>54.017722183068</v>
       </c>
       <c r="C6" t="n">
-        <v>387.6234460677682</v>
+        <v>389.8775387967189</v>
       </c>
       <c r="D6" t="n">
-        <v>92.82031844571895</v>
+        <v>91.00899393138359</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.03260296288517</v>
+        <v>26.40999499194344</v>
       </c>
       <c r="C7" t="n">
-        <v>431.4830247549943</v>
+        <v>401.95892604518</v>
       </c>
       <c r="D7" t="n">
-        <v>50.783845245279</v>
+        <v>49.70588626601601</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>293.9892587752286</v>
+        <v>279.3023131196963</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>122.8078020719377</v>
+        <v>123.5843645059969</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>46.12250714551515</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3725,7 +3725,7 @@
         <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3767,7 +3767,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.746169312956581</v>
+        <v>4.863578126838698</v>
       </c>
       <c r="C2" t="n">
-        <v>5.009858534771474</v>
+        <v>11.13203721845458</v>
       </c>
       <c r="D2" t="n">
-        <v>4.884194828627882</v>
+        <v>13.14167476904781</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.148063976892021</v>
+        <v>2.054797944988574</v>
       </c>
       <c r="C2" t="n">
-        <v>4.922482989093507</v>
+        <v>4.94309969088269</v>
       </c>
       <c r="D2" t="n">
-        <v>13.25948449355742</v>
+        <v>12.13145638137784</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.27813769993811</v>
+        <v>12.40438224315845</v>
       </c>
       <c r="C3" t="n">
-        <v>23.92519155249477</v>
+        <v>24.3326168497572</v>
       </c>
       <c r="D3" t="n">
-        <v>62.03172869283472</v>
+        <v>71.2405221586698</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.14326271602458</v>
+        <v>40.27914480983814</v>
       </c>
       <c r="C4" t="n">
-        <v>100.7872010656818</v>
+        <v>114.8900068371872</v>
       </c>
       <c r="D4" t="n">
-        <v>148.3155709236784</v>
+        <v>159.9551717052286</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.66703296400687</v>
+        <v>30.43417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>318.3071494094222</v>
+        <v>331.1435006424492</v>
       </c>
       <c r="D5" t="n">
-        <v>139.2363681548039</v>
+        <v>137.7146592132214</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.53713916741002</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="C6" t="n">
-        <v>348.7805981492432</v>
+        <v>329.7013132649107</v>
       </c>
       <c r="D6" t="n">
-        <v>73.98254349663115</v>
+        <v>72.49323222928874</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.611268966847268</v>
+        <v>4.671155576806323</v>
       </c>
       <c r="C7" t="n">
-        <v>206.7285775786594</v>
+        <v>196.4280806657018</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3625112492411</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>90.45823346930109</v>
+        <v>91.04237335332795</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>19.52499834206056</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35653864755762</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4333,7 @@
         <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.81497376771187</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4375,7 +4375,7 @@
         <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.910522090193298</v>
+        <v>6.66704865954009</v>
       </c>
       <c r="C2" t="n">
-        <v>10.00302735857075</v>
+        <v>4.547455366071226</v>
       </c>
       <c r="D2" t="n">
-        <v>20.77378142186251</v>
+        <v>12.6046587748248</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.20803270230909</v>
+        <v>10.33780332571891</v>
       </c>
       <c r="C3" t="n">
-        <v>12.82162501746335</v>
+        <v>28.04853191033137</v>
       </c>
       <c r="D3" t="n">
-        <v>7.431830121148355</v>
+        <v>14.17643684932394</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39931895613191</v>
+        <v>13.39700115612584</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1493757115141</v>
+        <v>70.13724134677645</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576390465427283</v>
+        <v>1.576117783073628</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.237223091529233</v>
+        <v>4.819399480147592</v>
       </c>
       <c r="C2" t="n">
-        <v>8.1563599268825</v>
+        <v>6.364670366632072</v>
       </c>
       <c r="D2" t="n">
-        <v>28.24095446036375</v>
+        <v>19.04786895779661</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.19316761802514</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C3" t="n">
-        <v>29.20699420134261</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="D3" t="n">
-        <v>23.08579726536375</v>
+        <v>21.33828635180442</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.21767025290231</v>
+        <v>12.1118214272929</v>
       </c>
       <c r="C4" t="n">
-        <v>20.08852152429823</v>
+        <v>43.29114676646735</v>
       </c>
       <c r="D4" t="n">
-        <v>18.96540215063988</v>
+        <v>22.50067563363265</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4423558745172</v>
+        <v>15.43858827807958</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15209066835912</v>
+        <v>86.1310714461282</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251022289372043</v>
+        <v>3.250229111174649</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.777184328864979</v>
+        <v>5.312236827679491</v>
       </c>
       <c r="C2" t="n">
-        <v>9.043859851521617</v>
+        <v>10.66374356352885</v>
       </c>
       <c r="D2" t="n">
-        <v>30.73164838603791</v>
+        <v>18.90257029756809</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64062358698343</v>
+        <v>17.22476347101029</v>
       </c>
       <c r="C3" t="n">
-        <v>30.74342935848887</v>
+        <v>23.51776625523235</v>
       </c>
       <c r="D3" t="n">
-        <v>40.3203782134165</v>
+        <v>31.62209355378976</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.24840753137022</v>
+        <v>24.90006702281185</v>
       </c>
       <c r="C4" t="n">
-        <v>51.2933723037831</v>
+        <v>49.65974412391641</v>
       </c>
       <c r="D4" t="n">
-        <v>26.26567807941916</v>
+        <v>28.14179794223482</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.44365215132832</v>
+        <v>10.84831213192726</v>
       </c>
       <c r="C5" t="n">
-        <v>23.4392264388926</v>
+        <v>47.88474427463818</v>
       </c>
       <c r="D5" t="n">
-        <v>29.28062527916113</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73390993139347</v>
+        <v>16.72931610446757</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0768505815001</v>
+        <v>102.0488282372522</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183477482848367</v>
+        <v>4.182329026116894</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.025566498039423</v>
+        <v>6.627778751370216</v>
       </c>
       <c r="C2" t="n">
-        <v>13.7287598961874</v>
+        <v>8.50095337107313</v>
       </c>
       <c r="D2" t="n">
-        <v>27.86101809882023</v>
+        <v>33.50115865971816</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.44427404613408</v>
+        <v>17.69600236904876</v>
       </c>
       <c r="C3" t="n">
-        <v>33.241977265797</v>
+        <v>33.81629967278138</v>
       </c>
       <c r="D3" t="n">
-        <v>54.70789081915351</v>
+        <v>38.9508401659922</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.72437524148068</v>
+        <v>29.21386643527233</v>
       </c>
       <c r="C4" t="n">
-        <v>65.61314431792708</v>
+        <v>54.79035762631024</v>
       </c>
       <c r="D4" t="n">
-        <v>39.79416144394021</v>
+        <v>37.13951565165684</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.62990647769474</v>
+        <v>24.05281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>61.92373644536757</v>
+        <v>71.56940763959248</v>
       </c>
       <c r="D5" t="n">
-        <v>31.75953823238432</v>
+        <v>33.55122779263475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.27046364475338</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>25.03652995370216</v>
+        <v>45.08185457901354</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05462608782696</v>
+        <v>18.05053855212882</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7849416205854</v>
+        <v>117.758275316269</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01820869594232</v>
+        <v>6.01684618404294</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.665085164131596</v>
+        <v>6.857507714163971</v>
       </c>
       <c r="C2" t="n">
-        <v>15.44780012632356</v>
+        <v>11.07018711308703</v>
       </c>
       <c r="D2" t="n">
-        <v>26.48166257435346</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.13364086096458</v>
+        <v>18.12797135891735</v>
       </c>
       <c r="C3" t="n">
-        <v>41.79299976978672</v>
+        <v>31.28829933434585</v>
       </c>
       <c r="D3" t="n">
-        <v>59.94060608278901</v>
+        <v>52.44005362234338</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.21989579021806</v>
+        <v>23.0239471599962</v>
       </c>
       <c r="C4" t="n">
-        <v>62.39693883881453</v>
+        <v>59.09139431861551</v>
       </c>
       <c r="D4" t="n">
-        <v>50.00433756810704</v>
+        <v>41.60646770597982</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.72116795646068</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="C5" t="n">
-        <v>69.60591223109887</v>
+        <v>64.99169802113886</v>
       </c>
       <c r="D5" t="n">
-        <v>30.9495963763807</v>
+        <v>31.3668391506856</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.92078153559227</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>42.2642386678252</v>
+        <v>54.42023874180921</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>31.396291581813</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>18.32530264747096</v>
+        <v>27.36818075128833</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053137287620399</v>
+        <v>7.051453810749226</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12316207144124</v>
+        <v>66.107379475774</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408210804762749</v>
+        <v>4.407158631718267</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.714352475793183</v>
+        <v>5.805074175211389</v>
       </c>
       <c r="C2" t="n">
-        <v>8.450884238156544</v>
+        <v>8.492117641734909</v>
       </c>
       <c r="D2" t="n">
-        <v>24.22953334081128</v>
+        <v>28.13983444682633</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0521968592411</v>
+        <v>21.67698930976957</v>
       </c>
       <c r="C3" t="n">
-        <v>53.55433726666351</v>
+        <v>38.86739161113123</v>
       </c>
       <c r="D3" t="n">
-        <v>67.70132168486005</v>
+        <v>65.42366701100745</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.89105136702439</v>
+        <v>30.68157925312132</v>
       </c>
       <c r="C4" t="n">
-        <v>88.62432875776805</v>
+        <v>71.10111398466675</v>
       </c>
       <c r="D4" t="n">
-        <v>69.81207924899068</v>
+        <v>59.43598776280615</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.61794557879453</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>97.16847902782808</v>
+        <v>91.0325558762855</v>
       </c>
       <c r="D5" t="n">
-        <v>42.21515128261285</v>
+        <v>39.44171401811561</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.09815907489146</v>
+        <v>21.05161602216436</v>
       </c>
       <c r="C6" t="n">
-        <v>81.75111308033615</v>
+        <v>83.28067600355268</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>42.57937968088841</v>
+        <v>57.25159912085699</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>22.36421270274234</v>
+        <v>29.12354564648163</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
         <v>23.27821981539612</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269922933812081</v>
+        <v>7.269229688170401</v>
       </c>
       <c r="C21" t="n">
-        <v>75.42545043830035</v>
+        <v>75.41825801476791</v>
       </c>
       <c r="D21" t="n">
-        <v>5.45244220035906</v>
+        <v>5.4519222661278</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.699626260229481</v>
+        <v>5.193445355465627</v>
       </c>
       <c r="C2" t="n">
-        <v>15.36926030998382</v>
+        <v>14.99815967777852</v>
       </c>
       <c r="D2" t="n">
-        <v>30.85043985825177</v>
+        <v>27.59692796637784</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.91689560250429</v>
+        <v>20.74923772925634</v>
       </c>
       <c r="C3" t="n">
-        <v>41.37084825696059</v>
+        <v>35.40182221513998</v>
       </c>
       <c r="D3" t="n">
-        <v>71.05889883338413</v>
+        <v>72.25663103256525</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.24688600431823</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C4" t="n">
-        <v>114.4688370720654</v>
+        <v>85.31878423756905</v>
       </c>
       <c r="D4" t="n">
-        <v>86.39085273060658</v>
+        <v>77.23998237932204</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.07293673421731</v>
+        <v>37.65002445786519</v>
       </c>
       <c r="C5" t="n">
-        <v>133.8122120888403</v>
+        <v>113.6863841517807</v>
       </c>
       <c r="D5" t="n">
-        <v>57.70222131710629</v>
+        <v>51.88536616944394</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.5510068084565</v>
       </c>
       <c r="C6" t="n">
-        <v>119.50716629026</v>
+        <v>116.5687954114493</v>
       </c>
       <c r="D6" t="n">
-        <v>39.40637110076273</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -6448,10 +6448,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="C7" t="n">
-        <v>82.82318157337367</v>
+        <v>91.14742035768236</v>
       </c>
       <c r="D7" t="n">
         <v>36.05173919535137</v>
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>40.38910055271378</v>
+        <v>53.57397222074844</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.07031028627404</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,7 +6490,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>26.90479583488384</v>
@@ -6507,7 +6507,7 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
         <v>26.03889435973815</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.471136847388815</v>
+        <v>7.472261929748029</v>
       </c>
       <c r="C21" t="n">
-        <v>84.05028953312417</v>
+        <v>84.06294670966534</v>
       </c>
       <c r="D21" t="n">
-        <v>6.537244741465213</v>
+        <v>6.538229188529526</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_15_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497655263382</v>
+        <v>10.84497649922367</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907270995363</v>
+        <v>37.78907252384718</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.363287708300325</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C2" t="n">
-        <v>9.908779578963058</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="D2" t="n">
-        <v>29.92170653003429</v>
+        <v>31.46108693029329</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03608798534566</v>
+        <v>13.82300767579509</v>
       </c>
       <c r="C3" t="n">
-        <v>47.50677140850316</v>
+        <v>30.11511082777091</v>
       </c>
       <c r="D3" t="n">
-        <v>76.7481267794944</v>
+        <v>100.9531164276995</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.5817030291954</v>
+        <v>29.52017171899734</v>
       </c>
       <c r="C4" t="n">
-        <v>86.07178472672636</v>
+        <v>54.52234050305086</v>
       </c>
       <c r="D4" t="n">
-        <v>93.99743394311086</v>
+        <v>126.3126413760989</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.06851102178158</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="C5" t="n">
-        <v>135.9720570381833</v>
+        <v>100.2609842962055</v>
       </c>
       <c r="D5" t="n">
-        <v>65.58074664368695</v>
+        <v>92.30882789180636</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.57366912111219</v>
+        <v>34.05290086950487</v>
       </c>
       <c r="C6" t="n">
-        <v>147.0795505640317</v>
+        <v>117.2933252171835</v>
       </c>
       <c r="D6" t="n">
-        <v>46.08814597586652</v>
+        <v>56.47307319138928</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.58965482182061</v>
+        <v>23.95464398362217</v>
       </c>
       <c r="C7" t="n">
-        <v>129.7742837812731</v>
+        <v>91.32708018755953</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>41.80085375142069</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>86.61959994569608</v>
+        <v>57.49605429921444</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>47.8140584399324</v>
+        <v>35.94374694788421</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -926,7 +926,7 @@
         <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.658786659856551</v>
+        <v>7.679329043599275</v>
       </c>
       <c r="C21" t="n">
-        <v>92.86278825076069</v>
+        <v>93.11186465364121</v>
       </c>
       <c r="D21" t="n">
-        <v>7.658786659856551</v>
+        <v>8.639245174049185</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.590472338608838</v>
+        <v>4.762458113301277</v>
       </c>
       <c r="C2" t="n">
-        <v>15.90038581798134</v>
+        <v>10.37216449536755</v>
       </c>
       <c r="D2" t="n">
-        <v>33.4285093296039</v>
+        <v>47.11014533598745</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25559856046944</v>
+        <v>12.9443434804942</v>
       </c>
       <c r="C3" t="n">
-        <v>42.7992911666397</v>
+        <v>36.41793108903543</v>
       </c>
       <c r="D3" t="n">
-        <v>81.03836424705297</v>
+        <v>101.8317806230004</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.82044764777662</v>
+        <v>27.64405185618169</v>
       </c>
       <c r="C4" t="n">
-        <v>100.3405058602495</v>
+        <v>64.79633022799374</v>
       </c>
       <c r="D4" t="n">
-        <v>106.4410860944392</v>
+        <v>144.6909583995992</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.82998738737862</v>
+        <v>40.37437433715008</v>
       </c>
       <c r="C5" t="n">
-        <v>146.1822331623501</v>
+        <v>99.30378028456489</v>
       </c>
       <c r="D5" t="n">
-        <v>81.26416621902975</v>
+        <v>111.7474324358932</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.79129831628549</v>
+        <v>41.861722109084</v>
       </c>
       <c r="C6" t="n">
-        <v>176.3425043845164</v>
+        <v>137.3789014983689</v>
       </c>
       <c r="D6" t="n">
-        <v>53.85671555957153</v>
+        <v>70.27939115621218</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.29128563518759</v>
+        <v>31.4404702285041</v>
       </c>
       <c r="C7" t="n">
-        <v>165.9457961965426</v>
+        <v>127.0194997231566</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>47.13076203777662</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.02765316663493</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="C8" t="n">
-        <v>125.3397294011903</v>
+        <v>87.53753404916685</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>73.66249374504666</v>
+        <v>52.14062057254808</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>36.15776794741003</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.827821240408505</v>
+        <v>7.858609340772745</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7831984702595</v>
+        <v>101.1795952624491</v>
       </c>
       <c r="D21" t="n">
-        <v>8.806298895459568</v>
+        <v>9.823261675965931</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.158904259367741</v>
+        <v>6.262568605390403</v>
       </c>
       <c r="C2" t="n">
-        <v>13.17603593869644</v>
+        <v>15.6058615067073</v>
       </c>
       <c r="D2" t="n">
-        <v>29.7940793284822</v>
+        <v>44.66264830930014</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.33552103514093</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C3" t="n">
-        <v>51.17850782238622</v>
+        <v>37.89546138392688</v>
       </c>
       <c r="D3" t="n">
-        <v>85.62312602588557</v>
+        <v>111.3596420927157</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.85498874387451</v>
+        <v>25.95937279569416</v>
       </c>
       <c r="C4" t="n">
-        <v>101.6933541967016</v>
+        <v>75.73398140100744</v>
       </c>
       <c r="D4" t="n">
-        <v>116.1918042930185</v>
+        <v>156.1901692594421</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.95899724726245</v>
+        <v>40.54618018539328</v>
       </c>
       <c r="C5" t="n">
-        <v>160.147594255261</v>
+        <v>107.9186163893307</v>
       </c>
       <c r="D5" t="n">
-        <v>94.59139130418019</v>
+        <v>132.3150468398639</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.67433147075987</v>
+        <v>46.93343074922303</v>
       </c>
       <c r="C6" t="n">
-        <v>197.474623718429</v>
+        <v>145.0669677703257</v>
       </c>
       <c r="D6" t="n">
-        <v>63.79887456047898</v>
+        <v>83.84419918579036</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.03473068920969</v>
+        <v>38.98618308334508</v>
       </c>
       <c r="C7" t="n">
-        <v>202.7161747114026</v>
+        <v>156.7831448728071</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>54.49681506274045</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.37112599440107</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>162.3908877594649</v>
+        <v>122.502478535917</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7562488319063</v>
+        <v>13.53437385074652</v>
       </c>
       <c r="C9" t="n">
-        <v>105.6124910320548</v>
+        <v>75.43749359432489</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>60.21549543997811</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,10 +1556,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.978984375821277</v>
+        <v>8.021161116815639</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7162890735872</v>
+        <v>109.2883202166131</v>
       </c>
       <c r="D21" t="n">
-        <v>9.973730469776596</v>
+        <v>11.0290965356215</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.656249434793374</v>
+        <v>5.639158813193679</v>
       </c>
       <c r="C2" t="n">
-        <v>9.275552309723864</v>
+        <v>10.73639289364312</v>
       </c>
       <c r="D2" t="n">
-        <v>24.8215272064721</v>
+        <v>36.79884919828319</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.28214680621311</v>
+        <v>17.37693436516854</v>
       </c>
       <c r="C3" t="n">
-        <v>72.72786993060372</v>
+        <v>57.1426251256856</v>
       </c>
       <c r="D3" t="n">
-        <v>91.42034621946299</v>
+        <v>120.0137481056513</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.96388062358789</v>
+        <v>19.47591095684822</v>
       </c>
       <c r="C4" t="n">
-        <v>132.6557132932375</v>
+        <v>95.31199411909735</v>
       </c>
       <c r="D4" t="n">
-        <v>109.1978336479642</v>
+        <v>149.515266618268</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.90680038802134</v>
+        <v>26.43355693684537</v>
       </c>
       <c r="C5" t="n">
-        <v>117.9815303578605</v>
+        <v>86.6637785923872</v>
       </c>
       <c r="D5" t="n">
-        <v>62.63550353094652</v>
+        <v>85.65748719553422</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.93464917663875</v>
+        <v>24.19124518034566</v>
       </c>
       <c r="C6" t="n">
-        <v>133.5147425344535</v>
+        <v>103.2454973171158</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="C7" t="n">
-        <v>114.2037651919187</v>
+        <v>86.11694512112172</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>77.77405313043232</v>
+        <v>55.57673753741193</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>45.92812110007426</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,10 +1853,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.085052197370977</v>
+        <v>3.318307240354219</v>
       </c>
       <c r="C2" t="n">
-        <v>4.57985304031137</v>
+        <v>4.805655012288137</v>
       </c>
       <c r="D2" t="n">
-        <v>17.58899186928585</v>
+        <v>25.29374785221482</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.60612354861455</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="C3" t="n">
-        <v>55.88107932572845</v>
+        <v>50.42747082863742</v>
       </c>
       <c r="D3" t="n">
-        <v>90.48277716190728</v>
+        <v>122.9540824798705</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.87676711981719</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C4" t="n">
-        <v>159.9041208246077</v>
+        <v>121.5266213178957</v>
       </c>
       <c r="D4" t="n">
-        <v>126.4657940179614</v>
+        <v>169.8079916650496</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.63744166415923</v>
+        <v>28.8879261974624</v>
       </c>
       <c r="C5" t="n">
-        <v>172.7139648696201</v>
+        <v>127.9708132485718</v>
       </c>
       <c r="D5" t="n">
-        <v>78.9079717288374</v>
+        <v>109.8821117978243</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.56358960216246</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C6" t="n">
-        <v>161.2481334317216</v>
+        <v>121.6002523957142</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>46.49066253460771</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="C7" t="n">
-        <v>143.7877505116921</v>
+        <v>111.5088677437612</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>101.8906854852552</v>
+        <v>73.68507394224434</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.627557767191965</v>
+        <v>2.76067454434203</v>
       </c>
       <c r="C2" t="n">
-        <v>4.936227456952962</v>
+        <v>10.30147866066178</v>
       </c>
       <c r="D2" t="n">
-        <v>20.82090531166635</v>
+        <v>25.56372847088269</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.80046853632642</v>
+        <v>15.01583113645496</v>
       </c>
       <c r="C3" t="n">
-        <v>36.86953503298896</v>
+        <v>34.00774047510951</v>
       </c>
       <c r="D3" t="n">
-        <v>84.9211764173491</v>
+        <v>115.1688231851933</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.31368590593603</v>
+        <v>30.63052837250048</v>
       </c>
       <c r="C4" t="n">
-        <v>149.8343346221482</v>
+        <v>123.5941819830394</v>
       </c>
       <c r="D4" t="n">
-        <v>139.3306159344116</v>
+        <v>189.0924618195696</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.11068511533519</v>
+        <v>33.33033455917922</v>
       </c>
       <c r="C5" t="n">
-        <v>228.624496626476</v>
+        <v>174.0147805777472</v>
       </c>
       <c r="D5" t="n">
-        <v>99.40195505498957</v>
+        <v>139.8008730847458</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>33.36862271964485</v>
       </c>
       <c r="C6" t="n">
-        <v>212.8507562623425</v>
+        <v>160.6041069377357</v>
       </c>
       <c r="D6" t="n">
-        <v>50.11331156327844</v>
+        <v>65.12717920432492</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.73316991308989</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="C7" t="n">
-        <v>182.2948407153647</v>
+        <v>141.7516057730842</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>140.4439178310274</v>
+        <v>106.3969074477481</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>79.87499321752047</v>
+        <v>61.79218225299847</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.23445777486574</v>
+        <v>1.656208377064369</v>
       </c>
       <c r="C2" t="n">
-        <v>2.440624792757571</v>
+        <v>4.916592502868026</v>
       </c>
       <c r="D2" t="n">
-        <v>14.70559886191297</v>
+        <v>17.85406374943249</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02488784997144</v>
+        <v>14.34824269756713</v>
       </c>
       <c r="C3" t="n">
-        <v>32.12278488295564</v>
+        <v>38.76430810218531</v>
       </c>
       <c r="D3" t="n">
-        <v>84.99480749516761</v>
+        <v>113.9023686467149</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.75962034784233</v>
+        <v>33.45108952680157</v>
       </c>
       <c r="C4" t="n">
-        <v>145.0355518437898</v>
+        <v>121.7435875605342</v>
       </c>
       <c r="D4" t="n">
-        <v>149.0302832523701</v>
+        <v>202.6464706244011</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.11697651218817</v>
+        <v>35.02384934900497</v>
       </c>
       <c r="C5" t="n">
-        <v>277.8100566092412</v>
+        <v>215.0027472300515</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2490233973053</v>
+        <v>147.605767333508</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>27.53213261789756</v>
       </c>
       <c r="C6" t="n">
-        <v>241.1074186859742</v>
+        <v>189.0620276407381</v>
       </c>
       <c r="D6" t="n">
-        <v>49.06676851055134</v>
+        <v>62.87308647537424</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.665486074759095</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>186.2473569726624</v>
+        <v>144.0272969515283</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>98.71964040053801</v>
+        <v>76.77267047210057</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.691952205044754</v>
+        <v>2.273727683035613</v>
       </c>
       <c r="C2" t="n">
-        <v>5.133558745506572</v>
+        <v>10.34565730735289</v>
       </c>
       <c r="D2" t="n">
-        <v>11.72501283181966</v>
+        <v>15.56560985083318</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.06706194352505</v>
+        <v>10.22490233973053</v>
       </c>
       <c r="C3" t="n">
-        <v>21.24011158137974</v>
+        <v>29.1628155546515</v>
       </c>
       <c r="D3" t="n">
-        <v>78.7656183117216</v>
+        <v>103.2749497482432</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.60722846950582</v>
+        <v>30.88578277560466</v>
       </c>
       <c r="C4" t="n">
-        <v>114.8517186767216</v>
+        <v>109.7466306146382</v>
       </c>
       <c r="D4" t="n">
-        <v>154.8500836431452</v>
+        <v>210.840136964045</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.19185137961819</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="C5" t="n">
-        <v>275.1593378077748</v>
+        <v>220.8441460703201</v>
       </c>
       <c r="D5" t="n">
-        <v>123.8965602759475</v>
+        <v>177.9663150873406</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>34.73717901936489</v>
       </c>
       <c r="C6" t="n">
-        <v>325.7969026451211</v>
+        <v>255.1552465860418</v>
       </c>
       <c r="D6" t="n">
-        <v>63.23535137824131</v>
+        <v>86.74231840872694</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>254.0389994463131</v>
+        <v>199.2427513337774</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>154.129480828228</v>
+        <v>120.7500588838364</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>62.56874468705769</v>
+        <v>52.47343304428775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.858448404139212</v>
+        <v>1.575705065316131</v>
       </c>
       <c r="C2" t="n">
-        <v>3.408628029144925</v>
+        <v>5.159084185816988</v>
       </c>
       <c r="D2" t="n">
-        <v>9.953939973358411</v>
+        <v>12.20606920690059</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.56989669454866</v>
+        <v>9.272607066611124</v>
       </c>
       <c r="C3" t="n">
-        <v>20.85722997672349</v>
+        <v>34.59188035913636</v>
       </c>
       <c r="D3" t="n">
-        <v>72.34989706446869</v>
+        <v>94.9693641703152</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.12751369502762</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C4" t="n">
-        <v>93.43587425628169</v>
+        <v>96.53721525399736</v>
       </c>
       <c r="D4" t="n">
-        <v>159.3425611377786</v>
+        <v>213.6479353981909</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.38882281527331</v>
+        <v>44.57134577280519</v>
       </c>
       <c r="C5" t="n">
-        <v>259.623180388069</v>
+        <v>221.3350199224435</v>
       </c>
       <c r="D5" t="n">
-        <v>138.0091835244954</v>
+        <v>199.9820073550753</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.28311285838414</v>
+        <v>39.80888765950392</v>
       </c>
       <c r="C6" t="n">
-        <v>374.6624128763019</v>
+        <v>296.8157104157552</v>
       </c>
       <c r="D6" t="n">
-        <v>74.46556336712058</v>
+        <v>103.1649940053676</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.3727863901733</v>
+        <v>13.71403368062369</v>
       </c>
       <c r="C7" t="n">
-        <v>321.0521159904962</v>
+        <v>253.4401333467226</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>48.44826745687584</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>196.2710010330223</v>
+        <v>155.1308634865597</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>66.56249434793372</v>
+        <v>58.13124506386212</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.78227299383546</v>
+        <v>1.891827826083604</v>
       </c>
       <c r="C2" t="n">
-        <v>8.239808481743479</v>
+        <v>7.124543089719102</v>
       </c>
       <c r="D2" t="n">
-        <v>16.13306002388784</v>
+        <v>11.86834799663969</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.130253649495335</v>
+        <v>7.417103905584653</v>
       </c>
       <c r="C3" t="n">
-        <v>17.40147805777471</v>
+        <v>27.92581344730052</v>
       </c>
       <c r="D3" t="n">
-        <v>65.30585728649783</v>
+        <v>85.24024442122931</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.51191682673587</v>
+        <v>22.69211643596077</v>
       </c>
       <c r="C4" t="n">
-        <v>76.05304940488766</v>
+        <v>91.86605967719103</v>
       </c>
       <c r="D4" t="n">
-        <v>158.3598316858275</v>
+        <v>211.6186628935127</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.50524988145118</v>
+        <v>43.44233591292137</v>
       </c>
       <c r="C5" t="n">
-        <v>224.2802630351839</v>
+        <v>203.0254252382404</v>
       </c>
       <c r="D5" t="n">
-        <v>154.821612959722</v>
+        <v>218.2916020392783</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.017722183068</v>
+        <v>46.41015922285948</v>
       </c>
       <c r="C6" t="n">
-        <v>389.8775387967189</v>
+        <v>318.5516045877796</v>
       </c>
       <c r="D6" t="n">
-        <v>91.00899393138359</v>
+        <v>129.8920935057828</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.40999499194344</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>401.95892604518</v>
+        <v>319.6747239614378</v>
       </c>
       <c r="D7" t="n">
-        <v>49.70588626601601</v>
+        <v>60.30581622876881</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>279.3023131196963</v>
+        <v>222.5572958142307</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>123.5843645059969</v>
+        <v>103.0609287487174</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>46.12250714551515</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.863578126838698</v>
+        <v>4.228387362191013</v>
       </c>
       <c r="C2" t="n">
-        <v>11.13203721845458</v>
+        <v>4.993168823799278</v>
       </c>
       <c r="D2" t="n">
-        <v>13.14167476904781</v>
+        <v>20.56663265626643</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.054797944988574</v>
+        <v>1.381319019875262</v>
       </c>
       <c r="C2" t="n">
-        <v>4.94309969088269</v>
+        <v>4.217588137444298</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13145638137784</v>
+        <v>8.829838851995813</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.40438224315845</v>
+        <v>9.896016858807849</v>
       </c>
       <c r="C3" t="n">
-        <v>24.3326168497572</v>
+        <v>32.41240045570844</v>
       </c>
       <c r="D3" t="n">
-        <v>71.2405221586698</v>
+        <v>91.40071126537805</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.27914480983814</v>
+        <v>32.45559735469531</v>
       </c>
       <c r="C4" t="n">
-        <v>114.8900068371872</v>
+        <v>128.3546766009322</v>
       </c>
       <c r="D4" t="n">
-        <v>159.9551717052286</v>
+        <v>214.1329187640888</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.43417883165113</v>
+        <v>26.53173170727006</v>
       </c>
       <c r="C5" t="n">
-        <v>331.1435006424492</v>
+        <v>282.7678825156876</v>
       </c>
       <c r="D5" t="n">
-        <v>137.7146592132214</v>
+        <v>196.7422399310609</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.38242394076653</v>
+        <v>15.17487426454295</v>
       </c>
       <c r="C6" t="n">
-        <v>329.7013132649107</v>
+        <v>266.7477234777882</v>
       </c>
       <c r="D6" t="n">
-        <v>72.49323222928874</v>
+        <v>97.32850390362032</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.671155576806323</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>196.4280806657018</v>
+        <v>156.4837118230118</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>91.04237335332795</v>
+        <v>75.93818492349078</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>35.16718451382499</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>19.52499834206056</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
         <v>18.93300447639974</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.66704865954009</v>
+        <v>5.782493978013713</v>
       </c>
       <c r="C2" t="n">
-        <v>4.547455366071226</v>
+        <v>5.086434855702724</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6046587748248</v>
+        <v>23.84370649304228</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.33780332571891</v>
+        <v>8.98790023237955</v>
       </c>
       <c r="C3" t="n">
-        <v>28.04853191033137</v>
+        <v>12.58109682992288</v>
       </c>
       <c r="D3" t="n">
-        <v>14.17643684932394</v>
+        <v>20.41053477129119</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39700115612584</v>
+        <v>13.39688971815934</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13724134677645</v>
+        <v>70.13665793624595</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576117783073628</v>
+        <v>1.576104672724628</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.819399480147592</v>
+        <v>3.955461500410399</v>
       </c>
       <c r="C2" t="n">
-        <v>6.364670366632072</v>
+        <v>4.754604131667302</v>
       </c>
       <c r="D2" t="n">
-        <v>19.04786895779661</v>
+        <v>23.74651347032185</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.91198686398306</v>
+        <v>15.54597489674824</v>
       </c>
       <c r="C3" t="n">
-        <v>21.5935407549086</v>
+        <v>17.11677122354314</v>
       </c>
       <c r="D3" t="n">
-        <v>21.33828635180442</v>
+        <v>35.5049057240859</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.1118214272929</v>
+        <v>10.58029500866788</v>
       </c>
       <c r="C4" t="n">
-        <v>43.29114676646735</v>
+        <v>19.73116535995239</v>
       </c>
       <c r="D4" t="n">
-        <v>22.50067563363265</v>
+        <v>25.76793199336603</v>
       </c>
     </row>
     <row r="5">
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43858827807958</v>
+        <v>15.43840704617777</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1310714461282</v>
+        <v>86.13006036288651</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250229111174649</v>
+        <v>3.250190957090057</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.312236827679491</v>
+        <v>3.952516257297659</v>
       </c>
       <c r="C2" t="n">
-        <v>10.66374356352885</v>
+        <v>8.906415172927064</v>
       </c>
       <c r="D2" t="n">
-        <v>18.90257029756809</v>
+        <v>35.48527077000096</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.22476347101029</v>
+        <v>14.50532233024662</v>
       </c>
       <c r="C3" t="n">
-        <v>23.51776625523235</v>
+        <v>17.95616551067416</v>
       </c>
       <c r="D3" t="n">
-        <v>31.62209355378976</v>
+        <v>46.26486056263094</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.90006702281185</v>
+        <v>21.64557338323367</v>
       </c>
       <c r="C4" t="n">
-        <v>49.65974412391641</v>
+        <v>33.3489877655599</v>
       </c>
       <c r="D4" t="n">
-        <v>28.14179794223482</v>
+        <v>37.75212621910685</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.84831213192726</v>
+        <v>9.670214886831083</v>
       </c>
       <c r="C5" t="n">
-        <v>47.88474427463818</v>
+        <v>23.09561474240622</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>31.88225669541517</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5207,10 +5207,10 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
         <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72931610446757</v>
+        <v>16.73151726641083</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0488282372522</v>
+        <v>102.0622553251061</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182329026116894</v>
+        <v>5.019455179923249</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.627778751370216</v>
+        <v>5.064836406209294</v>
       </c>
       <c r="C2" t="n">
-        <v>8.50095337107313</v>
+        <v>7.37783399741478</v>
       </c>
       <c r="D2" t="n">
-        <v>33.50115865971816</v>
+        <v>38.90764326700534</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.69600236904876</v>
+        <v>13.98008730847458</v>
       </c>
       <c r="C3" t="n">
-        <v>33.81629967278138</v>
+        <v>27.5331143656018</v>
       </c>
       <c r="D3" t="n">
-        <v>38.9508401659922</v>
+        <v>62.93984531926301</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.21386643527233</v>
+        <v>25.24466046700248</v>
       </c>
       <c r="C4" t="n">
-        <v>54.79035762631024</v>
+        <v>39.81968688425063</v>
       </c>
       <c r="D4" t="n">
-        <v>37.13951565165684</v>
+        <v>51.65072846812894</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.05281875404686</v>
+        <v>20.96031348566941</v>
       </c>
       <c r="C5" t="n">
-        <v>71.56940763959248</v>
+        <v>43.6632291463769</v>
       </c>
       <c r="D5" t="n">
-        <v>33.55122779263475</v>
+        <v>37.62548076525901</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="C6" t="n">
-        <v>45.08185457901354</v>
+        <v>25.07678160957628</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.76234460677682</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05053855212882</v>
+        <v>18.05563471547624</v>
       </c>
       <c r="C21" t="n">
-        <v>117.758275316269</v>
+        <v>117.7915217152498</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01684618404294</v>
+        <v>6.87833703446714</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.857507714163971</v>
+        <v>5.073672135547516</v>
       </c>
       <c r="C2" t="n">
-        <v>11.07018711308703</v>
+        <v>5.607742886657781</v>
       </c>
       <c r="D2" t="n">
-        <v>30.54217107911827</v>
+        <v>31.21761349964007</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.12797135891735</v>
+        <v>14.13716694115407</v>
       </c>
       <c r="C3" t="n">
-        <v>31.28829933434585</v>
+        <v>26.46791810649401</v>
       </c>
       <c r="D3" t="n">
-        <v>52.44005362234338</v>
+        <v>73.86178852900878</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.0239471599962</v>
+        <v>18.9909275909503</v>
       </c>
       <c r="C4" t="n">
-        <v>59.09139431861551</v>
+        <v>46.9540474510122</v>
       </c>
       <c r="D4" t="n">
-        <v>41.60646770597982</v>
+        <v>61.52907386826035</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.66578917439536</v>
+        <v>18.18687622117217</v>
       </c>
       <c r="C5" t="n">
-        <v>64.99169802113886</v>
+        <v>44.05592822807562</v>
       </c>
       <c r="D5" t="n">
-        <v>31.3668391506856</v>
+        <v>37.87091769132071</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.67298020349458</v>
+        <v>10.34467555964864</v>
       </c>
       <c r="C6" t="n">
-        <v>54.42023874180921</v>
+        <v>32.68434456978482</v>
       </c>
       <c r="D6" t="n">
-        <v>31.396291581813</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>27.36818075128833</v>
+        <v>18.56484908730718</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.66194429903638</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051453810749226</v>
+        <v>7.055909023957779</v>
       </c>
       <c r="C21" t="n">
-        <v>66.107379475774</v>
+        <v>66.14914709960418</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407158631718267</v>
+        <v>5.291931767968334</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.805074175211389</v>
+        <v>4.397247967321463</v>
       </c>
       <c r="C2" t="n">
-        <v>8.492117641734909</v>
+        <v>4.661338099763856</v>
       </c>
       <c r="D2" t="n">
-        <v>28.13983444682633</v>
+        <v>37.23867216978577</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.67698930976957</v>
+        <v>16.53754007803752</v>
       </c>
       <c r="C3" t="n">
-        <v>38.86739161113123</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D3" t="n">
-        <v>65.42366701100745</v>
+        <v>82.23609644623407</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.68157925312132</v>
+        <v>24.21088013443059</v>
       </c>
       <c r="C4" t="n">
-        <v>71.10111398466675</v>
+        <v>59.19349607985719</v>
       </c>
       <c r="D4" t="n">
-        <v>59.43598776280615</v>
+        <v>85.3698351181899</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.59340188618836</v>
+        <v>24.42097414313941</v>
       </c>
       <c r="C5" t="n">
-        <v>91.0325558762855</v>
+        <v>70.19496085364696</v>
       </c>
       <c r="D5" t="n">
-        <v>39.44171401811561</v>
+        <v>52.91620125890309</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.05161602216436</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="C6" t="n">
-        <v>83.28067600355268</v>
+        <v>54.66174867705392</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>37.6755498981756</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>57.25159912085699</v>
+        <v>35.15344004596554</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>29.12354564648163</v>
+        <v>22.44766125760332</v>
       </c>
       <c r="D8" t="n">
         <v>32.12769362147687</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269229688170401</v>
+        <v>7.277073768651075</v>
       </c>
       <c r="C21" t="n">
-        <v>75.41825801476791</v>
+        <v>75.49964034975491</v>
       </c>
       <c r="D21" t="n">
-        <v>5.4519222661278</v>
+        <v>6.367439547569691</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.193445355465627</v>
+        <v>3.566689409528662</v>
       </c>
       <c r="C2" t="n">
-        <v>14.99815967777852</v>
+        <v>9.800787331495908</v>
       </c>
       <c r="D2" t="n">
-        <v>27.59692796637784</v>
+        <v>38.5964292447591</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.74923772925634</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="C3" t="n">
-        <v>35.40182221513998</v>
+        <v>20.25836387713293</v>
       </c>
       <c r="D3" t="n">
-        <v>72.25663103256525</v>
+        <v>92.94696389956677</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.15227837181205</v>
+        <v>28.88203571123692</v>
       </c>
       <c r="C4" t="n">
-        <v>85.31878423756905</v>
+        <v>59.0786315984603</v>
       </c>
       <c r="D4" t="n">
-        <v>77.23998237932204</v>
+        <v>107.4238155463902</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.65002445786519</v>
+        <v>30.82687791334985</v>
       </c>
       <c r="C5" t="n">
-        <v>113.6863841517807</v>
+        <v>92.60335220308041</v>
       </c>
       <c r="D5" t="n">
-        <v>51.88536616944394</v>
+        <v>71.07853378746908</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.5510068084565</v>
+        <v>26.52584122104457</v>
       </c>
       <c r="C6" t="n">
-        <v>116.5687954114493</v>
+        <v>85.93728529124456</v>
       </c>
       <c r="D6" t="n">
-        <v>39.1246095096439</v>
+        <v>46.08814597586652</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>91.14742035768236</v>
+        <v>58.74876436983337</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>53.57397222074844</v>
+        <v>35.88287859022092</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>30.61874740004951</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.472261929748029</v>
+        <v>7.485396007384274</v>
       </c>
       <c r="C21" t="n">
-        <v>84.06294670966534</v>
+        <v>84.21070508307308</v>
       </c>
       <c r="D21" t="n">
-        <v>6.538229188529526</v>
+        <v>7.485396007384274</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_15_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_15_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497649922367</v>
+        <v>10.84497634259147</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907252384718</v>
+        <v>37.78907197806588</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.657010198319369</v>
+        <v>1.246819584393449</v>
       </c>
       <c r="C2" t="n">
-        <v>10.98281156740907</v>
+        <v>2.806816686441631</v>
       </c>
       <c r="D2" t="n">
-        <v>31.46108693029329</v>
+        <v>15.09437095279471</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.82300767579509</v>
+        <v>11.20174130545611</v>
       </c>
       <c r="C3" t="n">
-        <v>30.11511082777091</v>
+        <v>34.07646281440679</v>
       </c>
       <c r="D3" t="n">
-        <v>100.9531164276995</v>
+        <v>57.53041546886309</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.52017171899734</v>
+        <v>20.95638649485241</v>
       </c>
       <c r="C4" t="n">
-        <v>54.52234050305086</v>
+        <v>101.9868967602714</v>
       </c>
       <c r="D4" t="n">
-        <v>126.3126413760989</v>
+        <v>65.68972063885833</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.33095645398497</v>
+        <v>21.03394456348791</v>
       </c>
       <c r="C5" t="n">
-        <v>100.2609842962055</v>
+        <v>111.8456072063179</v>
       </c>
       <c r="D5" t="n">
-        <v>92.30882789180636</v>
+        <v>46.38757902566179</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.05290086950487</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C6" t="n">
-        <v>117.2933252171835</v>
+        <v>75.14984151698062</v>
       </c>
       <c r="D6" t="n">
-        <v>56.47307319138928</v>
+        <v>29.62521872335175</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.95464398362217</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>91.32708018755953</v>
+        <v>42.4596064609703</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>57.49605429921444</v>
+        <v>29.2069942013426</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.65583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.679329043599275</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.11186465364121</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.639245174049185</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.762458113301277</v>
+        <v>2.089159114637213</v>
       </c>
       <c r="C2" t="n">
-        <v>10.37216449536755</v>
+        <v>2.301216618754523</v>
       </c>
       <c r="D2" t="n">
-        <v>47.11014533598745</v>
+        <v>13.93787215719197</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.9443434804942</v>
+        <v>7.451465075233291</v>
       </c>
       <c r="C3" t="n">
-        <v>36.41793108903543</v>
+        <v>20.57743188101315</v>
       </c>
       <c r="D3" t="n">
-        <v>101.8317806230004</v>
+        <v>56.80883090624168</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.64405185618169</v>
+        <v>21.65833610338889</v>
       </c>
       <c r="C4" t="n">
-        <v>64.79633022799374</v>
+        <v>92.52972112526189</v>
       </c>
       <c r="D4" t="n">
-        <v>144.6909583995992</v>
+        <v>78.98847504058561</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="C5" t="n">
-        <v>99.30378028456489</v>
+        <v>155.0915935783899</v>
       </c>
       <c r="D5" t="n">
-        <v>111.7474324358932</v>
+        <v>58.78214379177778</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.861722109084</v>
+        <v>20.97111271041612</v>
       </c>
       <c r="C6" t="n">
-        <v>137.3789014983689</v>
+        <v>129.0870603883004</v>
       </c>
       <c r="D6" t="n">
-        <v>70.27939115621218</v>
+        <v>36.79001346894498</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.4404702285041</v>
+        <v>11.07902284242525</v>
       </c>
       <c r="C7" t="n">
-        <v>127.0194997231566</v>
+        <v>76.11588125795946</v>
       </c>
       <c r="D7" t="n">
-        <v>47.13076203777662</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.69247628885927</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>87.53753404916685</v>
+        <v>42.97600575340412</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>52.14062057254808</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.858609340772745</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1795952624491</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.823261675965931</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.262568605390403</v>
+        <v>1.093666942530947</v>
       </c>
       <c r="C2" t="n">
-        <v>15.6058615067073</v>
+        <v>0.9581857593448869</v>
       </c>
       <c r="D2" t="n">
-        <v>44.66264830930014</v>
+        <v>9.390416791120741</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.07335334037803</v>
+        <v>8.065057390387548</v>
       </c>
       <c r="C3" t="n">
-        <v>37.89546138392688</v>
+        <v>16.16447595042373</v>
       </c>
       <c r="D3" t="n">
-        <v>111.3596420927157</v>
+        <v>56.9119144151876</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.95937279569416</v>
+        <v>23.50893052589412</v>
       </c>
       <c r="C4" t="n">
-        <v>75.73398140100744</v>
+        <v>84.11908854297945</v>
       </c>
       <c r="D4" t="n">
-        <v>156.1901692594421</v>
+        <v>88.29249803373266</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.54618018539328</v>
+        <v>27.02260555939346</v>
       </c>
       <c r="C5" t="n">
-        <v>107.9186163893307</v>
+        <v>180.5434028109885</v>
       </c>
       <c r="D5" t="n">
-        <v>132.3150468398639</v>
+        <v>67.15154297048184</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.93343074922303</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="C6" t="n">
-        <v>145.0669677703257</v>
+        <v>169.3387162624196</v>
       </c>
       <c r="D6" t="n">
-        <v>83.84419918579036</v>
+        <v>37.55479493055324</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.98618308334508</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>156.7831448728071</v>
+        <v>73.48087041976102</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.03456645829366</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>122.502478535917</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>41.39048321104552</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.53437385074652</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>75.43749359432489</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.021161116815639</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2883202166131</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0290965356215</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.639158813193679</v>
+        <v>1.426479414270615</v>
       </c>
       <c r="C2" t="n">
-        <v>10.73639289364312</v>
+        <v>8.782714962191966</v>
       </c>
       <c r="D2" t="n">
-        <v>36.79884919828319</v>
+        <v>14.98048821910208</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.37693436516854</v>
+        <v>5.856125055832224</v>
       </c>
       <c r="C3" t="n">
-        <v>57.1426251256856</v>
+        <v>9.012443924985719</v>
       </c>
       <c r="D3" t="n">
-        <v>120.0137481056513</v>
+        <v>51.38958357879929</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.47591095684822</v>
+        <v>19.66735175917635</v>
       </c>
       <c r="C4" t="n">
-        <v>95.31199411909735</v>
+        <v>60.54634441630929</v>
       </c>
       <c r="D4" t="n">
-        <v>149.515266618268</v>
+        <v>97.3412666237755</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.43355693684537</v>
+        <v>31.75953823238432</v>
       </c>
       <c r="C5" t="n">
-        <v>86.6637785923872</v>
+        <v>170.676838383308</v>
       </c>
       <c r="D5" t="n">
-        <v>85.65748719553422</v>
+        <v>81.85321484157782</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.19124518034566</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="C6" t="n">
-        <v>103.2454973171158</v>
+        <v>228.870915300242</v>
       </c>
       <c r="D6" t="n">
-        <v>35.86422538384024</v>
+        <v>48.18123208132072</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.58859095865835</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>86.11694512112172</v>
+        <v>155.2859796238307</v>
       </c>
       <c r="D7" t="n">
-        <v>29.10489244010094</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>55.57673753741193</v>
+        <v>67.76022654711485</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.318307240354219</v>
+        <v>0.7255115534383928</v>
       </c>
       <c r="C2" t="n">
-        <v>4.805655012288137</v>
+        <v>4.057563261652067</v>
       </c>
       <c r="D2" t="n">
-        <v>25.29374785221482</v>
+        <v>10.49782820151114</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.79065105928395</v>
+        <v>5.532148313430777</v>
       </c>
       <c r="C3" t="n">
-        <v>50.42747082863742</v>
+        <v>22.32494279457247</v>
       </c>
       <c r="D3" t="n">
-        <v>122.9540824798705</v>
+        <v>51.62520302781852</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.69135567243478</v>
+        <v>16.73192612347839</v>
       </c>
       <c r="C4" t="n">
-        <v>121.5266213178957</v>
+        <v>43.57192660988194</v>
       </c>
       <c r="D4" t="n">
-        <v>169.8079916650496</v>
+        <v>100.8765401067683</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.8879261974624</v>
+        <v>33.08489763311751</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9708132485718</v>
+        <v>150.7473599870978</v>
       </c>
       <c r="D5" t="n">
-        <v>109.8821117978243</v>
+        <v>95.08226515630359</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.77993394999525</v>
+        <v>30.91327171132357</v>
       </c>
       <c r="C6" t="n">
-        <v>121.6002523957142</v>
+        <v>259.0999088617055</v>
       </c>
       <c r="D6" t="n">
-        <v>46.49066253460771</v>
+        <v>58.08313942635406</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.57051858935441</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>111.5088677437612</v>
+        <v>220.3228380393649</v>
       </c>
       <c r="D7" t="n">
-        <v>32.39865598784899</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>73.68507394224434</v>
+        <v>104.2272450213626</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>49.47812079863073</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.76067454434203</v>
+        <v>0.7530004891573036</v>
       </c>
       <c r="C2" t="n">
-        <v>10.30147866066178</v>
+        <v>8.986918484675302</v>
       </c>
       <c r="D2" t="n">
-        <v>25.56372847088269</v>
+        <v>13.08571514990573</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.01583113645496</v>
+        <v>3.995713156284519</v>
       </c>
       <c r="C3" t="n">
-        <v>34.00774047510951</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="D3" t="n">
-        <v>115.1688231851933</v>
+        <v>48.27253461781567</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.63052837250048</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C4" t="n">
-        <v>123.5941819830394</v>
+        <v>49.74908316500287</v>
       </c>
       <c r="D4" t="n">
-        <v>189.0924618195696</v>
+        <v>103.250406055637</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.33033455917922</v>
+        <v>30.23782929080177</v>
       </c>
       <c r="C5" t="n">
-        <v>174.0147805777472</v>
+        <v>117.5397438909494</v>
       </c>
       <c r="D5" t="n">
-        <v>139.8008730847458</v>
+        <v>107.3786551519949</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.36862271964485</v>
+        <v>37.15227837181205</v>
       </c>
       <c r="C6" t="n">
-        <v>160.6041069377357</v>
+        <v>251.3313392780005</v>
       </c>
       <c r="D6" t="n">
-        <v>65.12717920432492</v>
+        <v>71.40643752068752</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>141.7516057730842</v>
+        <v>293.5641620192897</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06981156465531</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>106.3969074477481</v>
+        <v>186.6744172240097</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>61.79218225299847</v>
+        <v>83.09218044433726</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86248287260999</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
         <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.656208377064369</v>
+        <v>0.5056000676871074</v>
       </c>
       <c r="C2" t="n">
-        <v>4.916592502868026</v>
+        <v>4.674100819919064</v>
       </c>
       <c r="D2" t="n">
-        <v>17.85406374943249</v>
+        <v>9.420850969952392</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.34824269756713</v>
+        <v>5.321072557017712</v>
       </c>
       <c r="C3" t="n">
-        <v>38.76430810218531</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="D3" t="n">
-        <v>113.9023686467149</v>
+        <v>53.01437602932776</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.45108952680157</v>
+        <v>21.31374265919825</v>
       </c>
       <c r="C4" t="n">
-        <v>121.7435875605342</v>
+        <v>70.97348678311465</v>
       </c>
       <c r="D4" t="n">
-        <v>202.6464706244011</v>
+        <v>107.6918326696496</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.02384934900497</v>
+        <v>23.14470212761856</v>
       </c>
       <c r="C5" t="n">
-        <v>215.0027472300515</v>
+        <v>194.6314823669302</v>
       </c>
       <c r="D5" t="n">
-        <v>147.605767333508</v>
+        <v>99.84374152190064</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.53213261789756</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>189.0620276407381</v>
+        <v>257.3690876591183</v>
       </c>
       <c r="D6" t="n">
-        <v>62.87308647537424</v>
+        <v>62.02780170201773</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>144.0272969515283</v>
+        <v>131.2714490302495</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>76.77267047210057</v>
+        <v>61.2512392679585</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
         <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.273727683035613</v>
+        <v>0.3514656781203581</v>
       </c>
       <c r="C2" t="n">
-        <v>10.34565730735289</v>
+        <v>2.534872572365265</v>
       </c>
       <c r="D2" t="n">
-        <v>15.56560985083318</v>
+        <v>7.12257959431061</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.22490233973053</v>
+        <v>3.524474258246049</v>
       </c>
       <c r="C3" t="n">
-        <v>29.1628155546515</v>
+        <v>22.37893891830604</v>
       </c>
       <c r="D3" t="n">
-        <v>103.2749497482432</v>
+        <v>48.36089191119788</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.88578277560466</v>
+        <v>14.81751810019711</v>
       </c>
       <c r="C4" t="n">
-        <v>109.7466306146382</v>
+        <v>67.70623042338129</v>
       </c>
       <c r="D4" t="n">
-        <v>210.840136964045</v>
+        <v>105.0754750378319</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.28249096357838</v>
+        <v>21.86843011209771</v>
       </c>
       <c r="C5" t="n">
-        <v>220.8441460703201</v>
+        <v>148.1457285708437</v>
       </c>
       <c r="D5" t="n">
-        <v>177.9663150873406</v>
+        <v>102.9607904828843</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.73717901936489</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>255.1552465860418</v>
+        <v>234.4658954667445</v>
       </c>
       <c r="D6" t="n">
-        <v>86.74231840872694</v>
+        <v>65.24793417194728</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>199.2427513337774</v>
+        <v>174.9886743003599</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>120.7500588838364</v>
+        <v>70.43058030266617</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>52.47343304428775</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.575705065316131</v>
+        <v>0.3544109212330985</v>
       </c>
       <c r="C2" t="n">
-        <v>5.159084185816988</v>
+        <v>4.019275101186442</v>
       </c>
       <c r="D2" t="n">
-        <v>12.20606920690059</v>
+        <v>8.418486563916399</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.272607066611124</v>
+        <v>2.248202242725196</v>
       </c>
       <c r="C3" t="n">
-        <v>34.59188035913636</v>
+        <v>14.7900291644782</v>
       </c>
       <c r="D3" t="n">
-        <v>94.9693641703152</v>
+        <v>42.83856107480958</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.12078032981814</v>
+        <v>10.55476956835746</v>
       </c>
       <c r="C4" t="n">
-        <v>96.53721525399736</v>
+        <v>60.90370058065513</v>
       </c>
       <c r="D4" t="n">
-        <v>213.6479353981909</v>
+        <v>105.8412382471444</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.57134577280519</v>
+        <v>22.67837196810132</v>
       </c>
       <c r="C5" t="n">
-        <v>221.3350199224435</v>
+        <v>136.659280431156</v>
       </c>
       <c r="D5" t="n">
-        <v>199.9820073550753</v>
+        <v>117.9078992800419</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.80888765950392</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="C6" t="n">
-        <v>296.8157104157552</v>
+        <v>238.5313127100306</v>
       </c>
       <c r="D6" t="n">
-        <v>103.1649940053676</v>
+        <v>82.2341329508256</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.71403368062369</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>253.4401333467226</v>
+        <v>261.7643721310313</v>
       </c>
       <c r="D7" t="n">
-        <v>48.44826745687584</v>
+        <v>45.03473068920969</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>155.1308634865597</v>
+        <v>154.2963779379499</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>58.13124506386212</v>
+        <v>59.57343244140068</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.891827826083604</v>
+        <v>0.2621266370338984</v>
       </c>
       <c r="C2" t="n">
-        <v>7.124543089719102</v>
+        <v>7.660577336237862</v>
       </c>
       <c r="D2" t="n">
-        <v>11.86834799663969</v>
+        <v>14.24810443173396</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.417103905584653</v>
+        <v>1.688606051304514</v>
       </c>
       <c r="C3" t="n">
-        <v>27.92581344730052</v>
+        <v>15.21218067730433</v>
       </c>
       <c r="D3" t="n">
-        <v>85.24024442122931</v>
+        <v>39.78041697608076</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.69211643596077</v>
+        <v>7.364089529555325</v>
       </c>
       <c r="C4" t="n">
-        <v>91.86605967719103</v>
+        <v>47.98782778358409</v>
       </c>
       <c r="D4" t="n">
-        <v>211.6186628935127</v>
+        <v>102.5612191672558</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.44233591292137</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C5" t="n">
-        <v>203.0254252382404</v>
+        <v>124.0438224315845</v>
       </c>
       <c r="D5" t="n">
-        <v>218.2916020392783</v>
+        <v>129.0998231084556</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.41015922285948</v>
+        <v>26.04282135055514</v>
       </c>
       <c r="C6" t="n">
-        <v>318.5516045877796</v>
+        <v>229.1124252354867</v>
       </c>
       <c r="D6" t="n">
-        <v>129.8920935057828</v>
+        <v>99.22033172970391</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>319.6747239614378</v>
+        <v>302.8465865629433</v>
       </c>
       <c r="D7" t="n">
-        <v>60.30581622876881</v>
+        <v>56.23352675155305</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>222.5572958142307</v>
+        <v>251.0967015766854</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>34.88149593188918</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>103.0609287487174</v>
+        <v>123.6953019965768</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.41779222031519</v>
+        <v>48.40016181936776</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.228387362191013</v>
+        <v>5.526257827205296</v>
       </c>
       <c r="C2" t="n">
-        <v>4.993168823799278</v>
+        <v>9.374708827852793</v>
       </c>
       <c r="D2" t="n">
-        <v>20.56663265626643</v>
+        <v>12.50255701358313</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.381319019875262</v>
+        <v>0.3956443248114646</v>
       </c>
       <c r="C2" t="n">
-        <v>4.217588137444298</v>
+        <v>8.851437301489241</v>
       </c>
       <c r="D2" t="n">
-        <v>8.829838851995813</v>
+        <v>13.80140922630166</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.896016858807849</v>
+        <v>1.276272015520854</v>
       </c>
       <c r="C3" t="n">
-        <v>32.41240045570844</v>
+        <v>22.46238747316702</v>
       </c>
       <c r="D3" t="n">
-        <v>91.40071126537805</v>
+        <v>41.3855744725243</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.45559735469531</v>
+        <v>5.360342465187585</v>
       </c>
       <c r="C4" t="n">
-        <v>128.3546766009322</v>
+        <v>43.01036692305276</v>
       </c>
       <c r="D4" t="n">
-        <v>214.1329187640888</v>
+        <v>99.57474265093698</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.53173170727006</v>
+        <v>16.02703127182918</v>
       </c>
       <c r="C5" t="n">
-        <v>282.7678825156876</v>
+        <v>105.9305772882309</v>
       </c>
       <c r="D5" t="n">
-        <v>196.7422399310609</v>
+        <v>134.3767170187822</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.17487426454295</v>
+        <v>26.76735115628929</v>
       </c>
       <c r="C6" t="n">
-        <v>266.7477234777882</v>
+        <v>215.5476172059085</v>
       </c>
       <c r="D6" t="n">
-        <v>97.32850390362032</v>
+        <v>115.1599874558551</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.611268966847268</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="C7" t="n">
-        <v>156.4837118230118</v>
+        <v>316.1414139738536</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>69.04926128279091</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>75.93818492349078</v>
+        <v>322.9459073119883</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>33.05937219280708</v>
+        <v>208.0077948372929</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>89.96735961717772</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.782493978013713</v>
+        <v>5.977861771158828</v>
       </c>
       <c r="C2" t="n">
-        <v>5.086434855702724</v>
+        <v>8.392961123605982</v>
       </c>
       <c r="D2" t="n">
-        <v>23.84370649304228</v>
+        <v>15.17487426454295</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.98790023237955</v>
+        <v>9.125344910974103</v>
       </c>
       <c r="C3" t="n">
-        <v>12.58109682992288</v>
+        <v>18.50594422505237</v>
       </c>
       <c r="D3" t="n">
-        <v>20.41053477129119</v>
+        <v>11.54535300194249</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39688971815934</v>
+        <v>11.67760427726848</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13665793624595</v>
+        <v>59.9450352899782</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576104672724628</v>
+        <v>0.7785069518178986</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.955461500410399</v>
+        <v>3.57356164345839</v>
       </c>
       <c r="C2" t="n">
-        <v>4.754604131667302</v>
+        <v>5.275912162622359</v>
       </c>
       <c r="D2" t="n">
-        <v>23.74651347032185</v>
+        <v>20.05906909317083</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.54597489674824</v>
+        <v>16.48845269282518</v>
       </c>
       <c r="C3" t="n">
-        <v>17.11677122354314</v>
+        <v>28.0387144332889</v>
       </c>
       <c r="D3" t="n">
-        <v>35.5049057240859</v>
+        <v>21.99605731364979</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.58029500866788</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C4" t="n">
-        <v>19.73116535995239</v>
+        <v>30.63052837250048</v>
       </c>
       <c r="D4" t="n">
-        <v>25.76793199336603</v>
+        <v>20.3310132072472</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43840704617777</v>
+        <v>13.62801221054386</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13006036288651</v>
+        <v>73.75159549235498</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250190957090057</v>
+        <v>1.60329555418163</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.952516257297659</v>
+        <v>2.045962215650353</v>
       </c>
       <c r="C2" t="n">
-        <v>8.906415172927064</v>
+        <v>6.042657119639118</v>
       </c>
       <c r="D2" t="n">
-        <v>35.48527077000096</v>
+        <v>15.63629568553895</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.50532233024662</v>
+        <v>14.17152811080271</v>
       </c>
       <c r="C3" t="n">
-        <v>17.95616551067416</v>
+        <v>23.31159923734051</v>
       </c>
       <c r="D3" t="n">
-        <v>46.26486056263094</v>
+        <v>33.52668410002858</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.64557338323367</v>
+        <v>23.78971036930871</v>
       </c>
       <c r="C4" t="n">
-        <v>33.3489877655599</v>
+        <v>55.14771379065608</v>
       </c>
       <c r="D4" t="n">
-        <v>37.75212621910685</v>
+        <v>27.13354304997335</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.670214886831083</v>
+        <v>10.40652566501619</v>
       </c>
       <c r="C5" t="n">
-        <v>23.09561474240622</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="D5" t="n">
-        <v>31.88225669541517</v>
+        <v>27.243498792849</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73151726641083</v>
+        <v>14.83710441340365</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0622553251061</v>
+        <v>87.37405932337704</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019455179923249</v>
+        <v>2.472850735567275</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.064836406209294</v>
+        <v>2.221695054710532</v>
       </c>
       <c r="C2" t="n">
-        <v>7.37783399741478</v>
+        <v>5.394703634836223</v>
       </c>
       <c r="D2" t="n">
-        <v>38.90764326700534</v>
+        <v>15.11498765458389</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.98008730847458</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5331143656018</v>
+        <v>23.43431770037137</v>
       </c>
       <c r="D3" t="n">
-        <v>62.93984531926301</v>
+        <v>38.25379929597697</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.24466046700248</v>
+        <v>25.92108463522854</v>
       </c>
       <c r="C4" t="n">
-        <v>39.81968688425063</v>
+        <v>57.08764725424778</v>
       </c>
       <c r="D4" t="n">
-        <v>51.65072846812894</v>
+        <v>37.8287025400381</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.96031348566941</v>
+        <v>23.88101290580367</v>
       </c>
       <c r="C5" t="n">
-        <v>43.6632291463769</v>
+        <v>73.21383504420589</v>
       </c>
       <c r="D5" t="n">
-        <v>37.62548076525901</v>
+        <v>30.67961575771283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.620145753914496</v>
+        <v>9.539642442166258</v>
       </c>
       <c r="C6" t="n">
-        <v>25.07678160957628</v>
+        <v>36.4277485660779</v>
       </c>
       <c r="D6" t="n">
-        <v>38.76234460677682</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05563471547624</v>
+        <v>16.07874263754331</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7915217152498</v>
+        <v>101.5499535002736</v>
       </c>
       <c r="D21" t="n">
-        <v>6.87833703446714</v>
+        <v>3.384998450009119</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.073672135547516</v>
+        <v>3.09643225919444</v>
       </c>
       <c r="C2" t="n">
-        <v>5.607742886657781</v>
+        <v>9.021279654323941</v>
       </c>
       <c r="D2" t="n">
-        <v>31.21761349964007</v>
+        <v>16.56404726605219</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.13716694115407</v>
+        <v>8.801368168572656</v>
       </c>
       <c r="C3" t="n">
-        <v>26.46791810649401</v>
+        <v>21.98133109808609</v>
       </c>
       <c r="D3" t="n">
-        <v>73.86178852900878</v>
+        <v>41.23340357836604</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.9909275909503</v>
+        <v>22.80698091735765</v>
       </c>
       <c r="C4" t="n">
-        <v>46.9540474510122</v>
+        <v>57.95551222480196</v>
       </c>
       <c r="D4" t="n">
-        <v>61.52907386826035</v>
+        <v>47.91125146265284</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.18687622117217</v>
+        <v>31.46501392111028</v>
       </c>
       <c r="C5" t="n">
-        <v>44.05592822807562</v>
+        <v>89.92808970900784</v>
       </c>
       <c r="D5" t="n">
-        <v>37.87091769132071</v>
+        <v>36.71736413883072</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.34467555964864</v>
+        <v>21.01136436629024</v>
       </c>
       <c r="C6" t="n">
-        <v>32.68434456978482</v>
+        <v>78.57123226628075</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>36.18623863083319</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>18.56484908730718</v>
+        <v>35.87207936547421</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055909023957779</v>
+        <v>17.34725400604287</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14914709960418</v>
+        <v>115.3592391401851</v>
       </c>
       <c r="D21" t="n">
-        <v>5.291931767968334</v>
+        <v>4.336813501510719</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.397247967321463</v>
+        <v>2.666426764734337</v>
       </c>
       <c r="C2" t="n">
-        <v>4.661338099763856</v>
+        <v>10.24748253692821</v>
       </c>
       <c r="D2" t="n">
-        <v>37.23867216978577</v>
+        <v>28.15161541927729</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.53754007803752</v>
+        <v>9.645671194224912</v>
       </c>
       <c r="C3" t="n">
-        <v>23.53249247079604</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D3" t="n">
-        <v>82.23609644623407</v>
+        <v>44.3848137089983</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.21088013443059</v>
+        <v>19.64182631886593</v>
       </c>
       <c r="C4" t="n">
-        <v>59.19349607985719</v>
+        <v>56.33464676509047</v>
       </c>
       <c r="D4" t="n">
-        <v>85.3698351181899</v>
+        <v>56.69200292943631</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.42097414313941</v>
+        <v>33.20761609614836</v>
       </c>
       <c r="C5" t="n">
-        <v>70.19496085364696</v>
+        <v>97.70844026516383</v>
       </c>
       <c r="D5" t="n">
-        <v>52.91620125890309</v>
+        <v>44.27682146153116</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.43525839034661</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C6" t="n">
-        <v>54.66174867705392</v>
+        <v>110.8128086214502</v>
       </c>
       <c r="D6" t="n">
-        <v>37.6755498981756</v>
+        <v>39.60762938013333</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>35.15344004596554</v>
+        <v>73.95996329943345</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>22.44766125760332</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.85168364786328</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.277073768651075</v>
+        <v>18.63623973815965</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49964034975491</v>
+        <v>128.6787981920547</v>
       </c>
       <c r="D21" t="n">
-        <v>6.367439547569691</v>
+        <v>5.324639925188471</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.566689409528662</v>
+        <v>2.444551783574558</v>
       </c>
       <c r="C2" t="n">
-        <v>9.800787331495908</v>
+        <v>6.311655990602745</v>
       </c>
       <c r="D2" t="n">
-        <v>38.5964292447591</v>
+        <v>22.01569226773472</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80122929985241</v>
+        <v>13.09160563613122</v>
       </c>
       <c r="C3" t="n">
-        <v>20.25836387713293</v>
+        <v>44.5860719883689</v>
       </c>
       <c r="D3" t="n">
-        <v>92.94696389956677</v>
+        <v>51.2030515149924</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.88203571123692</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C4" t="n">
-        <v>59.0786315984603</v>
+        <v>83.92764774065132</v>
       </c>
       <c r="D4" t="n">
-        <v>107.4238155463902</v>
+        <v>53.88420449529043</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.82687791334985</v>
+        <v>17.57328390601791</v>
       </c>
       <c r="C5" t="n">
-        <v>92.60335220308041</v>
+        <v>66.1943389588412</v>
       </c>
       <c r="D5" t="n">
-        <v>71.07853378746908</v>
+        <v>36.84008260186157</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.52584122104457</v>
+        <v>10.30442390377452</v>
       </c>
       <c r="C6" t="n">
-        <v>85.93728529124456</v>
+        <v>48.70450360768427</v>
       </c>
       <c r="D6" t="n">
-        <v>46.08814597586652</v>
+        <v>25.51954982419159</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.04961146902685</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>58.74876436983337</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>35.88287859022092</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>26.40312275801371</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.96708790860789</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.485396007384274</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.21070508307308</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.485396007384274</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
